--- a/results/02_taxa_assemblage/LDA_Method/ModelFinalized/tables/env_ord_pca/pca_loadings.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelFinalized/tables/env_ord_pca/pca_loadings.xlsx
@@ -462,19 +462,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6487066747422109</v>
+        <v>-0.5593321440147075</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1563064528879206</v>
+        <v>-0.3743452268733143</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3055409781305804</v>
+        <v>0.3030552726234476</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3048352249731319</v>
+        <v>0.4632422679855297</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6070157652228548</v>
+        <v>0.490486805812173</v>
       </c>
     </row>
     <row r="3">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1190437146397743</v>
+        <v>0.5720033119526516</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7623285653811135</v>
+        <v>-0.4569238991689541</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3056691120053395</v>
+        <v>-0.125618990521157</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1298362128553058</v>
+        <v>-0.2528154987599305</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5425796754449949</v>
+        <v>0.6199491546011259</v>
       </c>
     </row>
     <row r="4">
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.4464276832209609</v>
+        <v>-0.07737238124724825</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.6023203473131487</v>
+        <v>0.7565205793346175</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2092577095568265</v>
+        <v>-0.2487626097808029</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2739214875114943</v>
+        <v>0.04754344086824535</v>
       </c>
       <c r="F4" t="n">
-        <v>0.564881184442405</v>
+        <v>0.5979522663798482</v>
       </c>
     </row>
     <row r="5">
@@ -528,19 +528,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.5810637280734996</v>
+        <v>0.5931943556464295</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08741009801932281</v>
+        <v>0.1690185004311111</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3301630833147849</v>
+        <v>0.308288234588268</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7304172459552948</v>
+        <v>0.7212024637166801</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1104871210084471</v>
+        <v>-0.06617079177912007</v>
       </c>
     </row>
     <row r="6">
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1675574878092852</v>
+        <v>0.04575734734942637</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1548971438290249</v>
+        <v>0.2240436587824793</v>
       </c>
       <c r="D6" t="n">
-        <v>0.81265900232261</v>
+        <v>0.8575855055591057</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5307312963614871</v>
+        <v>-0.4462034875455243</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07642643599649625</v>
+        <v>0.1147181436393057</v>
       </c>
     </row>
     <row r="7">
@@ -580,19 +580,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.445477256917768</v>
+        <v>1.422042796685778</v>
       </c>
       <c r="C8" t="n">
-        <v>1.22397583212926</v>
+        <v>1.278288943570247</v>
       </c>
       <c r="D8" t="n">
-        <v>1.10646969229414</v>
+        <v>1.074747180272035</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7118622192098211</v>
+        <v>0.6955854758960043</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5337667235869409</v>
+        <v>0.5455168333493984</v>
       </c>
     </row>
     <row r="9">
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2878546983733239</v>
+        <v>0.2834911123715519</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2437445433939814</v>
+        <v>0.2548330861698105</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2203441790663009</v>
+        <v>0.2142560507768122</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1417614033104537</v>
+        <v>0.1386683303560421</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1062951758559402</v>
+        <v>0.1087514203257833</v>
       </c>
     </row>
     <row r="10">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2878546983733239</v>
+        <v>0.2834911123715519</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5315992417673053</v>
+        <v>0.5383241985413625</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7519434208336062</v>
+        <v>0.7525802493181747</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8937048241440599</v>
+        <v>0.8912485796742169</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
